--- a/public/report/DayReport.xlsx
+++ b/public/report/DayReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Test\19-5Restful+API\RestfulAPI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\test\SEEMS_EMS\public\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12AE22A4-DB1A-4799-8A90-5B6E004F5C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5C2684-01B0-46DF-96E1-A6A833C784A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="735" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日報" sheetId="2" r:id="rId1"/>
@@ -242,7 +242,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="0.0"/>
+    <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -867,10 +867,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -885,10 +885,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -915,10 +915,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -927,7 +927,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -939,6 +939,33 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -959,33 +986,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1310,25 +1310,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>24</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1691,78 +1691,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
-                <c:pt idx="0">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>95.5</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>95.5</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1887,78 +1815,6 @@
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="24"/>
-                <c:pt idx="0">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>99</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>99</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2083,78 +1939,6 @@
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="24"/>
-                <c:pt idx="0">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>100</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>100</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3846,41 +3630,41 @@
   <sheetData>
     <row r="2" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="3:13" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="47"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="40"/>
     </row>
     <row r="4" spans="3:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="34" t="s">
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="L4" s="39"/>
-      <c r="M4" s="40"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="49"/>
     </row>
     <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="35"/>
+      <c r="C5" s="44"/>
       <c r="D5" s="6">
         <v>1</v>
       </c>
@@ -3916,841 +3700,361 @@
       <c r="C6" s="13">
         <v>0</v>
       </c>
-      <c r="D6" s="14">
-        <v>1</v>
-      </c>
-      <c r="E6" s="15">
-        <v>1</v>
-      </c>
-      <c r="F6" s="15">
-        <v>1</v>
-      </c>
-      <c r="G6" s="15">
-        <v>1</v>
-      </c>
-      <c r="H6" s="15">
-        <v>1</v>
-      </c>
-      <c r="I6" s="15">
-        <v>1</v>
-      </c>
-      <c r="J6" s="9">
-        <v>1</v>
-      </c>
-      <c r="K6" s="16">
-        <v>100</v>
-      </c>
-      <c r="L6" s="17">
-        <v>99</v>
-      </c>
-      <c r="M6" s="9">
-        <v>95.5</v>
-      </c>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="9"/>
     </row>
     <row r="7" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C7" s="12">
         <v>1</v>
       </c>
-      <c r="D7" s="5">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4">
-        <v>0</v>
-      </c>
-      <c r="K7" s="11">
-        <v>100</v>
-      </c>
-      <c r="L7" s="10">
-        <v>99</v>
-      </c>
-      <c r="M7" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="4"/>
     </row>
     <row r="8" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C8" s="12">
         <v>2</v>
       </c>
-      <c r="D8" s="5">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4">
-        <v>0</v>
-      </c>
-      <c r="K8" s="11">
-        <v>100</v>
-      </c>
-      <c r="L8" s="10">
-        <v>99</v>
-      </c>
-      <c r="M8" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="4"/>
     </row>
     <row r="9" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C9" s="12">
         <v>3</v>
       </c>
-      <c r="D9" s="5">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4">
-        <v>0</v>
-      </c>
-      <c r="K9" s="11">
-        <v>100</v>
-      </c>
-      <c r="L9" s="10">
-        <v>99</v>
-      </c>
-      <c r="M9" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="4"/>
     </row>
     <row r="10" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C10" s="12">
         <v>4</v>
       </c>
-      <c r="D10" s="5">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4">
-        <v>0</v>
-      </c>
-      <c r="K10" s="11">
-        <v>100</v>
-      </c>
-      <c r="L10" s="10">
-        <v>99</v>
-      </c>
-      <c r="M10" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="4"/>
     </row>
     <row r="11" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C11" s="12">
         <v>5</v>
       </c>
-      <c r="D11" s="5">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3">
-        <v>0</v>
-      </c>
-      <c r="I11" s="3">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4">
-        <v>0</v>
-      </c>
-      <c r="K11" s="11">
-        <v>100</v>
-      </c>
-      <c r="L11" s="10">
-        <v>99</v>
-      </c>
-      <c r="M11" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="4"/>
     </row>
     <row r="12" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C12" s="12">
         <v>6</v>
       </c>
-      <c r="D12" s="5">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4">
-        <v>0</v>
-      </c>
-      <c r="K12" s="11">
-        <v>100</v>
-      </c>
-      <c r="L12" s="10">
-        <v>99</v>
-      </c>
-      <c r="M12" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="4"/>
     </row>
     <row r="13" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C13" s="12">
         <v>7</v>
       </c>
-      <c r="D13" s="5">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3">
-        <v>0</v>
-      </c>
-      <c r="I13" s="3">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4">
-        <v>0</v>
-      </c>
-      <c r="K13" s="11">
-        <v>100</v>
-      </c>
-      <c r="L13" s="10">
-        <v>99</v>
-      </c>
-      <c r="M13" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="4"/>
     </row>
     <row r="14" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C14" s="12">
         <v>8</v>
       </c>
-      <c r="D14" s="5">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4">
-        <v>0</v>
-      </c>
-      <c r="K14" s="11">
-        <v>100</v>
-      </c>
-      <c r="L14" s="10">
-        <v>99</v>
-      </c>
-      <c r="M14" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="4"/>
     </row>
     <row r="15" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C15" s="12">
         <v>9</v>
       </c>
-      <c r="D15" s="5">
-        <v>1</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="4">
-        <v>0</v>
-      </c>
-      <c r="K15" s="11">
-        <v>100</v>
-      </c>
-      <c r="L15" s="10">
-        <v>99</v>
-      </c>
-      <c r="M15" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="4"/>
     </row>
     <row r="16" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C16" s="12">
         <v>10</v>
       </c>
-      <c r="D16" s="5">
-        <v>1</v>
-      </c>
-      <c r="E16" s="3">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3">
-        <v>0</v>
-      </c>
-      <c r="G16" s="3">
-        <v>0</v>
-      </c>
-      <c r="H16" s="3">
-        <v>0</v>
-      </c>
-      <c r="I16" s="3">
-        <v>0</v>
-      </c>
-      <c r="J16" s="4">
-        <v>0</v>
-      </c>
-      <c r="K16" s="11">
-        <v>100</v>
-      </c>
-      <c r="L16" s="10">
-        <v>99</v>
-      </c>
-      <c r="M16" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="4"/>
     </row>
     <row r="17" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C17" s="12">
         <v>11</v>
       </c>
-      <c r="D17" s="5">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>0</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
-      <c r="I17" s="3">
-        <v>0</v>
-      </c>
-      <c r="J17" s="4">
-        <v>0</v>
-      </c>
-      <c r="K17" s="11">
-        <v>100</v>
-      </c>
-      <c r="L17" s="10">
-        <v>99</v>
-      </c>
-      <c r="M17" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="4"/>
     </row>
     <row r="18" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C18" s="12">
         <v>12</v>
       </c>
-      <c r="D18" s="5">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
-      <c r="J18" s="4">
-        <v>0</v>
-      </c>
-      <c r="K18" s="11">
-        <v>100</v>
-      </c>
-      <c r="L18" s="10">
-        <v>99</v>
-      </c>
-      <c r="M18" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="4"/>
     </row>
     <row r="19" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C19" s="12">
         <v>13</v>
       </c>
-      <c r="D19" s="5">
-        <v>1</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0</v>
-      </c>
-      <c r="G19" s="3">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3">
-        <v>0</v>
-      </c>
-      <c r="J19" s="4">
-        <v>0</v>
-      </c>
-      <c r="K19" s="11">
-        <v>100</v>
-      </c>
-      <c r="L19" s="10">
-        <v>99</v>
-      </c>
-      <c r="M19" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="4"/>
     </row>
     <row r="20" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C20" s="12">
         <v>14</v>
       </c>
-      <c r="D20" s="5">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4">
-        <v>0</v>
-      </c>
-      <c r="K20" s="11">
-        <v>100</v>
-      </c>
-      <c r="L20" s="10">
-        <v>99</v>
-      </c>
-      <c r="M20" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="4"/>
     </row>
     <row r="21" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C21" s="12">
         <v>15</v>
       </c>
-      <c r="D21" s="5">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
-      <c r="J21" s="4">
-        <v>0</v>
-      </c>
-      <c r="K21" s="11">
-        <v>100</v>
-      </c>
-      <c r="L21" s="10">
-        <v>99</v>
-      </c>
-      <c r="M21" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D21" s="5"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="4"/>
     </row>
     <row r="22" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C22" s="12">
         <v>16</v>
       </c>
-      <c r="D22" s="5">
-        <v>1</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="4">
-        <v>0</v>
-      </c>
-      <c r="K22" s="11">
-        <v>100</v>
-      </c>
-      <c r="L22" s="10">
-        <v>99</v>
-      </c>
-      <c r="M22" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="4"/>
     </row>
     <row r="23" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C23" s="12">
         <v>17</v>
       </c>
-      <c r="D23" s="5">
-        <v>1</v>
-      </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
-      <c r="J23" s="4">
-        <v>0</v>
-      </c>
-      <c r="K23" s="11">
-        <v>100</v>
-      </c>
-      <c r="L23" s="10">
-        <v>99</v>
-      </c>
-      <c r="M23" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="4"/>
     </row>
     <row r="24" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C24" s="12">
         <v>18</v>
       </c>
-      <c r="D24" s="5">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4">
-        <v>0</v>
-      </c>
-      <c r="K24" s="11">
-        <v>100</v>
-      </c>
-      <c r="L24" s="10">
-        <v>99</v>
-      </c>
-      <c r="M24" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D24" s="5"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="4"/>
     </row>
     <row r="25" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C25" s="12">
         <v>19</v>
       </c>
-      <c r="D25" s="5">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3">
-        <v>0</v>
-      </c>
-      <c r="F25" s="3">
-        <v>0</v>
-      </c>
-      <c r="G25" s="3">
-        <v>0</v>
-      </c>
-      <c r="H25" s="3">
-        <v>0</v>
-      </c>
-      <c r="I25" s="3">
-        <v>0</v>
-      </c>
-      <c r="J25" s="4">
-        <v>0</v>
-      </c>
-      <c r="K25" s="11">
-        <v>100</v>
-      </c>
-      <c r="L25" s="10">
-        <v>99</v>
-      </c>
-      <c r="M25" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="4"/>
     </row>
     <row r="26" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C26" s="12">
         <v>20</v>
       </c>
-      <c r="D26" s="5">
-        <v>1</v>
-      </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
-      <c r="J26" s="4">
-        <v>0</v>
-      </c>
-      <c r="K26" s="11">
-        <v>100</v>
-      </c>
-      <c r="L26" s="10">
-        <v>99</v>
-      </c>
-      <c r="M26" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D26" s="5"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="4"/>
     </row>
     <row r="27" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C27" s="12">
         <v>21</v>
       </c>
-      <c r="D27" s="5">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
-      <c r="J27" s="4">
-        <v>0</v>
-      </c>
-      <c r="K27" s="11">
-        <v>100</v>
-      </c>
-      <c r="L27" s="10">
-        <v>99</v>
-      </c>
-      <c r="M27" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D27" s="5"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="4"/>
     </row>
     <row r="28" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C28" s="12">
         <v>22</v>
       </c>
-      <c r="D28" s="5">
-        <v>1</v>
-      </c>
-      <c r="E28" s="3">
-        <v>0</v>
-      </c>
-      <c r="F28" s="3">
-        <v>0</v>
-      </c>
-      <c r="G28" s="3">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3">
-        <v>0</v>
-      </c>
-      <c r="I28" s="3">
-        <v>0</v>
-      </c>
-      <c r="J28" s="4">
-        <v>0</v>
-      </c>
-      <c r="K28" s="11">
-        <v>100</v>
-      </c>
-      <c r="L28" s="10">
-        <v>99</v>
-      </c>
-      <c r="M28" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D28" s="5"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="4"/>
     </row>
     <row r="29" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C29" s="12">
         <v>23</v>
       </c>
-      <c r="D29" s="5">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="4">
-        <v>0</v>
-      </c>
-      <c r="K29" s="11">
-        <v>100</v>
-      </c>
-      <c r="L29" s="10">
-        <v>99</v>
-      </c>
-      <c r="M29" s="4">
-        <v>95.5</v>
-      </c>
+      <c r="D29" s="5"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="4"/>
     </row>
     <row r="30" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C30" s="24" t="s">
@@ -4758,43 +4062,43 @@
       </c>
       <c r="D30" s="21">
         <f t="shared" ref="D30:J30" si="0">SUM(D6:D29)</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E30" s="22">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="22">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="22">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" s="22">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" s="22">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" s="25">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" s="26">
         <f>MAX(K6:K29)</f>
-        <v>100</v>
-      </c>
-      <c r="L30" s="27">
+        <v>0</v>
+      </c>
+      <c r="L30" s="27" t="e">
         <f>AVERAGE(L6:L29)</f>
-        <v>99</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="M30" s="23">
         <f>MIN(M6:M29)</f>
-        <v>95.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4804,18 +4108,18 @@
     </row>
     <row r="32" spans="3:14" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C32" s="1"/>
-      <c r="D32" s="45" t="s">
+      <c r="D32" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="47"/>
-      <c r="I32" s="45" t="s">
+      <c r="E32" s="39"/>
+      <c r="F32" s="39"/>
+      <c r="G32" s="40"/>
+      <c r="I32" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="J32" s="46"/>
-      <c r="K32" s="46"/>
-      <c r="L32" s="47"/>
+      <c r="J32" s="39"/>
+      <c r="K32" s="39"/>
+      <c r="L32" s="40"/>
       <c r="N32" s="2"/>
     </row>
     <row r="33" spans="3:22" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4824,20 +4128,16 @@
         <v>5</v>
       </c>
       <c r="E33" s="57"/>
-      <c r="F33" s="48">
-        <v>1234</v>
-      </c>
-      <c r="G33" s="49"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="42"/>
       <c r="I33" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="J33" s="32">
-        <v>34</v>
-      </c>
-      <c r="K33" s="48" t="s">
+      <c r="J33" s="32"/>
+      <c r="K33" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="L33" s="49"/>
+      <c r="L33" s="42"/>
     </row>
     <row r="34" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C34" s="1"/>
@@ -4845,20 +4145,16 @@
         <v>6</v>
       </c>
       <c r="E34" s="55"/>
-      <c r="F34" s="41">
-        <v>899</v>
-      </c>
-      <c r="G34" s="42"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="35"/>
       <c r="I34" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="J34" s="5">
-        <v>5</v>
-      </c>
-      <c r="K34" s="41" t="s">
+      <c r="J34" s="5"/>
+      <c r="K34" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="L34" s="42"/>
+      <c r="L34" s="35"/>
     </row>
     <row r="35" spans="3:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C35" s="1"/>
@@ -4866,21 +4162,16 @@
         <v>7</v>
       </c>
       <c r="E35" s="53"/>
-      <c r="F35" s="50">
-        <f>F33-F34</f>
-        <v>335</v>
-      </c>
+      <c r="F35" s="50"/>
       <c r="G35" s="51"/>
       <c r="I35" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="J35" s="6">
-        <v>30.9</v>
-      </c>
-      <c r="K35" s="43" t="s">
+      <c r="J35" s="6"/>
+      <c r="K35" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="L35" s="44"/>
+      <c r="L35" s="37"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>

--- a/public/report/DayReport.xlsx
+++ b/public/report/DayReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\test\SEEMS_EMS\public\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5C2684-01B0-46DF-96E1-A6A833C784A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C786B82-64C2-4F0D-B58E-24C68FCB5671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="735" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日報" sheetId="2" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>SBSPM (%)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -111,108 +111,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>XXYYZZ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve">MW </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>E-dReg</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>AA</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>BB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>CC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>日 日報</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>時數</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -236,6 +134,18 @@
     <t>%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>日報</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E-dReg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>花蓮和平10MW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -244,7 +154,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,19 +176,6 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -840,7 +737,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1011,6 +908,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -3630,19 +3530,23 @@
   <sheetData>
     <row r="2" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="3:13" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
+      <c r="C3" s="58" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="59"/>
       <c r="H3" s="39"/>
       <c r="I3" s="39"/>
       <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="40"/>
+      <c r="K3" s="59" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="59"/>
+      <c r="M3" s="60"/>
     </row>
     <row r="4" spans="3:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C4" s="43" t="s">
@@ -4109,7 +4013,7 @@
     <row r="32" spans="3:14" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C32" s="1"/>
       <c r="D32" s="38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E32" s="39"/>
       <c r="F32" s="39"/>
@@ -4131,11 +4035,11 @@
       <c r="F33" s="41"/>
       <c r="G33" s="42"/>
       <c r="I33" s="28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J33" s="32"/>
       <c r="K33" s="41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L33" s="42"/>
     </row>
@@ -4148,7 +4052,7 @@
       <c r="F34" s="34"/>
       <c r="G34" s="35"/>
       <c r="I34" s="33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="34" t="s">
@@ -4165,11 +4069,11 @@
       <c r="F35" s="50"/>
       <c r="G35" s="51"/>
       <c r="I35" s="29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J35" s="6"/>
       <c r="K35" s="36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L35" s="37"/>
       <c r="M35" s="2"/>
@@ -4193,7 +4097,6 @@
     <mergeCell ref="K35:L35"/>
     <mergeCell ref="I32:L32"/>
     <mergeCell ref="F33:G33"/>
-    <mergeCell ref="C3:M3"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:J4"/>
     <mergeCell ref="K4:M4"/>
@@ -4204,6 +4107,7 @@
     <mergeCell ref="D35:E35"/>
     <mergeCell ref="D34:E34"/>
     <mergeCell ref="D33:E33"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/report/DayReport.xlsx
+++ b/public/report/DayReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\test\SEEMS_EMS\public\report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hdrenewables-my.sharepoint.com/personal/hugo_huang_hdrenewables_com/Documents/2.案場資料/1.專案開發/3.表前-花蓮_10+10+40/8.報表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C786B82-64C2-4F0D-B58E-24C68FCB5671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="6_{DCBEEB1A-7347-4214-9C4B-83766357FDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-190" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日報" sheetId="2" r:id="rId1"/>
@@ -185,7 +185,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -398,9 +398,109 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -418,7 +518,7 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -427,11 +527,52 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -441,75 +582,21 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -519,7 +606,18 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -533,148 +631,6 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -683,53 +639,9 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -737,7 +649,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -770,10 +682,10 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -803,25 +715,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -830,87 +739,93 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1589,7 +1504,7 @@
             <c:numRef>
               <c:f>日報!$M$6:$M$29</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="24"/>
               </c:numCache>
             </c:numRef>
@@ -1928,7 +1843,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3517,58 +3432,58 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="C2:V40"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="8.75" style="1"/>
-    <col min="3" max="3" width="8.75" style="2" customWidth="1"/>
-    <col min="4" max="10" width="6.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.75" style="1"/>
+    <col min="1" max="2" width="8.7109375" style="1"/>
+    <col min="3" max="3" width="8.7109375" style="2" customWidth="1"/>
+    <col min="4" max="10" width="6.42578125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="3:13" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="58" t="s">
+    <row r="2" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="3:13" ht="15.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59" t="s">
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="59"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="59" t="s">
+      <c r="G3" s="33"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="59"/>
-      <c r="M3" s="60"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="34"/>
     </row>
-    <row r="4" spans="3:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="43" t="s">
+    <row r="4" spans="3:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="45" t="s">
+      <c r="D4" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="43" t="s">
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="L4" s="48"/>
-      <c r="M4" s="49"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="52"/>
     </row>
-    <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C5" s="44"/>
+    <row r="5" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="47"/>
       <c r="D5" s="6">
         <v>1</v>
       </c>
@@ -3600,7 +3515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C6" s="13">
         <v>0</v>
       </c>
@@ -3613,9 +3528,9 @@
       <c r="J6" s="9"/>
       <c r="K6" s="16"/>
       <c r="L6" s="17"/>
-      <c r="M6" s="9"/>
+      <c r="M6" s="17"/>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C7" s="12">
         <v>1</v>
       </c>
@@ -3628,9 +3543,9 @@
       <c r="J7" s="4"/>
       <c r="K7" s="11"/>
       <c r="L7" s="10"/>
-      <c r="M7" s="4"/>
+      <c r="M7" s="17"/>
     </row>
-    <row r="8" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C8" s="12">
         <v>2</v>
       </c>
@@ -3643,9 +3558,9 @@
       <c r="J8" s="4"/>
       <c r="K8" s="11"/>
       <c r="L8" s="10"/>
-      <c r="M8" s="4"/>
+      <c r="M8" s="17"/>
     </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C9" s="12">
         <v>3</v>
       </c>
@@ -3658,9 +3573,9 @@
       <c r="J9" s="4"/>
       <c r="K9" s="11"/>
       <c r="L9" s="10"/>
-      <c r="M9" s="4"/>
+      <c r="M9" s="17"/>
     </row>
-    <row r="10" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C10" s="12">
         <v>4</v>
       </c>
@@ -3673,9 +3588,9 @@
       <c r="J10" s="4"/>
       <c r="K10" s="11"/>
       <c r="L10" s="10"/>
-      <c r="M10" s="4"/>
+      <c r="M10" s="17"/>
     </row>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C11" s="12">
         <v>5</v>
       </c>
@@ -3688,9 +3603,9 @@
       <c r="J11" s="4"/>
       <c r="K11" s="11"/>
       <c r="L11" s="10"/>
-      <c r="M11" s="4"/>
+      <c r="M11" s="17"/>
     </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C12" s="12">
         <v>6</v>
       </c>
@@ -3703,9 +3618,9 @@
       <c r="J12" s="4"/>
       <c r="K12" s="11"/>
       <c r="L12" s="10"/>
-      <c r="M12" s="4"/>
+      <c r="M12" s="17"/>
     </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C13" s="12">
         <v>7</v>
       </c>
@@ -3718,9 +3633,9 @@
       <c r="J13" s="4"/>
       <c r="K13" s="11"/>
       <c r="L13" s="10"/>
-      <c r="M13" s="4"/>
+      <c r="M13" s="17"/>
     </row>
-    <row r="14" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C14" s="12">
         <v>8</v>
       </c>
@@ -3733,9 +3648,9 @@
       <c r="J14" s="4"/>
       <c r="K14" s="11"/>
       <c r="L14" s="10"/>
-      <c r="M14" s="4"/>
+      <c r="M14" s="17"/>
     </row>
-    <row r="15" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C15" s="12">
         <v>9</v>
       </c>
@@ -3748,9 +3663,9 @@
       <c r="J15" s="4"/>
       <c r="K15" s="11"/>
       <c r="L15" s="10"/>
-      <c r="M15" s="4"/>
+      <c r="M15" s="17"/>
     </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C16" s="12">
         <v>10</v>
       </c>
@@ -3763,9 +3678,9 @@
       <c r="J16" s="4"/>
       <c r="K16" s="11"/>
       <c r="L16" s="10"/>
-      <c r="M16" s="4"/>
+      <c r="M16" s="17"/>
     </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C17" s="12">
         <v>11</v>
       </c>
@@ -3778,9 +3693,9 @@
       <c r="J17" s="4"/>
       <c r="K17" s="11"/>
       <c r="L17" s="10"/>
-      <c r="M17" s="4"/>
+      <c r="M17" s="17"/>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C18" s="12">
         <v>12</v>
       </c>
@@ -3793,9 +3708,9 @@
       <c r="J18" s="4"/>
       <c r="K18" s="11"/>
       <c r="L18" s="10"/>
-      <c r="M18" s="4"/>
+      <c r="M18" s="17"/>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C19" s="12">
         <v>13</v>
       </c>
@@ -3808,9 +3723,9 @@
       <c r="J19" s="4"/>
       <c r="K19" s="11"/>
       <c r="L19" s="10"/>
-      <c r="M19" s="4"/>
+      <c r="M19" s="17"/>
     </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C20" s="12">
         <v>14</v>
       </c>
@@ -3823,9 +3738,9 @@
       <c r="J20" s="4"/>
       <c r="K20" s="11"/>
       <c r="L20" s="10"/>
-      <c r="M20" s="4"/>
+      <c r="M20" s="17"/>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C21" s="12">
         <v>15</v>
       </c>
@@ -3838,9 +3753,9 @@
       <c r="J21" s="4"/>
       <c r="K21" s="11"/>
       <c r="L21" s="10"/>
-      <c r="M21" s="4"/>
+      <c r="M21" s="17"/>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C22" s="12">
         <v>16</v>
       </c>
@@ -3853,9 +3768,9 @@
       <c r="J22" s="4"/>
       <c r="K22" s="11"/>
       <c r="L22" s="10"/>
-      <c r="M22" s="4"/>
+      <c r="M22" s="17"/>
     </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C23" s="12">
         <v>17</v>
       </c>
@@ -3868,9 +3783,9 @@
       <c r="J23" s="4"/>
       <c r="K23" s="11"/>
       <c r="L23" s="10"/>
-      <c r="M23" s="4"/>
+      <c r="M23" s="17"/>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C24" s="12">
         <v>18</v>
       </c>
@@ -3883,9 +3798,9 @@
       <c r="J24" s="4"/>
       <c r="K24" s="11"/>
       <c r="L24" s="10"/>
-      <c r="M24" s="4"/>
+      <c r="M24" s="17"/>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C25" s="12">
         <v>19</v>
       </c>
@@ -3898,9 +3813,9 @@
       <c r="J25" s="4"/>
       <c r="K25" s="11"/>
       <c r="L25" s="10"/>
-      <c r="M25" s="4"/>
+      <c r="M25" s="17"/>
     </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C26" s="12">
         <v>20</v>
       </c>
@@ -3913,9 +3828,9 @@
       <c r="J26" s="4"/>
       <c r="K26" s="11"/>
       <c r="L26" s="10"/>
-      <c r="M26" s="4"/>
+      <c r="M26" s="17"/>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C27" s="12">
         <v>21</v>
       </c>
@@ -3928,9 +3843,9 @@
       <c r="J27" s="4"/>
       <c r="K27" s="11"/>
       <c r="L27" s="10"/>
-      <c r="M27" s="4"/>
+      <c r="M27" s="17"/>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C28" s="12">
         <v>22</v>
       </c>
@@ -3943,9 +3858,9 @@
       <c r="J28" s="4"/>
       <c r="K28" s="11"/>
       <c r="L28" s="10"/>
-      <c r="M28" s="4"/>
+      <c r="M28" s="17"/>
     </row>
-    <row r="29" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C29" s="12">
         <v>23</v>
       </c>
@@ -3958,10 +3873,10 @@
       <c r="J29" s="4"/>
       <c r="K29" s="11"/>
       <c r="L29" s="10"/>
-      <c r="M29" s="4"/>
+      <c r="M29" s="17"/>
     </row>
-    <row r="30" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C30" s="24" t="s">
+    <row r="30" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C30" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="21">
@@ -3988,98 +3903,98 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J30" s="25">
+      <c r="J30" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K30" s="26">
+      <c r="K30" s="25">
         <f>MAX(K6:K29)</f>
         <v>0</v>
       </c>
-      <c r="L30" s="27" t="e">
+      <c r="L30" s="26" t="e">
         <f>AVERAGE(L6:L29)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M30" s="23">
+      <c r="M30" s="25">
         <f>MIN(M6:M29)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="3:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="K31" s="30"/>
-      <c r="L31" s="30"/>
+    <row r="31" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
       <c r="M31" s="2"/>
     </row>
-    <row r="32" spans="3:14" ht="15.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:14" ht="15.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1"/>
-      <c r="D32" s="38" t="s">
+      <c r="D32" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="40"/>
-      <c r="I32" s="38" t="s">
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="43"/>
+      <c r="I32" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="J32" s="39"/>
-      <c r="K32" s="39"/>
-      <c r="L32" s="40"/>
+      <c r="J32" s="37"/>
+      <c r="K32" s="37"/>
+      <c r="L32" s="43"/>
       <c r="N32" s="2"/>
     </row>
-    <row r="33" spans="3:22" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:22" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="1"/>
-      <c r="D33" s="56" t="s">
+      <c r="D33" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="E33" s="57"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="42"/>
-      <c r="I33" s="28" t="s">
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="45"/>
+      <c r="I33" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="J33" s="32"/>
-      <c r="K33" s="41" t="s">
+      <c r="J33" s="35"/>
+      <c r="K33" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="L33" s="42"/>
+      <c r="L33" s="54"/>
     </row>
-    <row r="34" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C34" s="1"/>
-      <c r="D34" s="54" t="s">
+      <c r="D34" s="60" t="s">
         <v>6</v>
       </c>
       <c r="E34" s="55"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="35"/>
-      <c r="I34" s="33" t="s">
+      <c r="F34" s="55"/>
+      <c r="G34" s="56"/>
+      <c r="I34" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="J34" s="5"/>
-      <c r="K34" s="34" t="s">
+      <c r="J34" s="11"/>
+      <c r="K34" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="L34" s="35"/>
+      <c r="L34" s="39"/>
     </row>
-    <row r="35" spans="3:22" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="3:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C35" s="1"/>
-      <c r="D35" s="52" t="s">
+      <c r="D35" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="53"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="51"/>
-      <c r="I35" s="29" t="s">
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
+      <c r="G35" s="58"/>
+      <c r="I35" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="J35" s="6"/>
-      <c r="K35" s="36" t="s">
+      <c r="J35" s="36"/>
+      <c r="K35" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="L35" s="37"/>
+      <c r="L35" s="41"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
-      <c r="P35" s="31"/>
+      <c r="P35" s="30"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
@@ -4087,27 +4002,27 @@
       <c r="U35" s="2"/>
       <c r="V35" s="2"/>
     </row>
-    <row r="37" spans="3:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="3:22" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="3:22" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="3:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="3:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="3:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="3:22" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="3:22" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D33:E33"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="D4:J4"/>
     <mergeCell ref="K4:M4"/>
     <mergeCell ref="K33:L33"/>
     <mergeCell ref="D32:G32"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="F33:G33"/>
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="F35:G35"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/report/DayReport.xlsx
+++ b/public/report/DayReport.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hdrenewables-my.sharepoint.com/personal/hugo_huang_hdrenewables_com/Documents/2.案場資料/1.專案開發/3.表前-花蓮_10+10+40/8.報表/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hdrenewables-my.sharepoint.com/personal/hugo_huang_hdrenewables_com/Documents/2.案場資料/1.專案開發/3.表前-花蓮三案/E-dReg-10M+10M/8.報表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="6_{DCBEEB1A-7347-4214-9C4B-83766357FDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="6_{DCBEEB1A-7347-4214-9C4B-83766357FDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43C1C5AB-6750-4881-99C3-B9BBAF8D97BA}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-190" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -154,7 +154,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,16 +176,30 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="35">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -645,11 +659,87 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -664,15 +754,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -682,12 +763,6 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -700,37 +775,16 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -739,19 +793,40 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -760,70 +835,118 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1124,27 +1247,6 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1381,8 +1483,8 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="8.314186201934394E-2"/>
-          <c:y val="3.5147661586967936E-2"/>
+          <c:x val="8.1375377878751473E-2"/>
+          <c:y val="2.6657441019367175E-2"/>
           <c:w val="0.90136211139546418"/>
           <c:h val="0.87941860749883671"/>
         </c:manualLayout>
@@ -3072,15 +3174,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
+      <xdr:colOff>260350</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>152716</xdr:rowOff>
+      <xdr:rowOff>6666</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>491490</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>56371</xdr:rowOff>
+      <xdr:colOff>504190</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>100821</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3110,15 +3212,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>64770</xdr:rowOff>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>131445</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>476251</xdr:colOff>
+      <xdr:colOff>527050</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>160830</xdr:rowOff>
+      <xdr:rowOff>33830</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3445,93 +3547,93 @@
   <sheetData>
     <row r="2" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="3:13" ht="15.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33" t="s">
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="33" t="s">
+      <c r="G3" s="51"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="33"/>
-      <c r="M3" s="34"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="53"/>
     </row>
     <row r="4" spans="3:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="46" t="s">
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="L4" s="51"/>
-      <c r="M4" s="52"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="59"/>
     </row>
     <row r="5" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="47"/>
-      <c r="D5" s="6">
+      <c r="C5" s="60"/>
+      <c r="D5" s="61">
         <v>1</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="62">
         <v>0.8</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="62">
         <v>0.6</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="62">
         <v>0.4</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="62">
         <v>0.2</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="62">
         <v>0</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="63">
         <v>-1</v>
       </c>
-      <c r="K5" s="18" t="s">
+      <c r="K5" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="L5" s="19" t="s">
+      <c r="L5" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="M5" s="20" t="s">
+      <c r="M5" s="66" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C6" s="13">
+      <c r="C6" s="67">
         <v>0</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C7" s="12">
+      <c r="C7" s="68">
         <v>1</v>
       </c>
       <c r="D7" s="5"/>
@@ -3541,12 +3643,12 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="4"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="17"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="12"/>
     </row>
     <row r="8" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C8" s="12">
+      <c r="C8" s="68">
         <v>2</v>
       </c>
       <c r="D8" s="5"/>
@@ -3556,12 +3658,12 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="4"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="17"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="12"/>
     </row>
     <row r="9" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C9" s="12">
+      <c r="C9" s="68">
         <v>3</v>
       </c>
       <c r="D9" s="5"/>
@@ -3571,12 +3673,12 @@
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="4"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="17"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="12"/>
     </row>
     <row r="10" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C10" s="12">
+      <c r="C10" s="68">
         <v>4</v>
       </c>
       <c r="D10" s="5"/>
@@ -3586,12 +3688,12 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="4"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="17"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="12"/>
     </row>
     <row r="11" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C11" s="12">
+      <c r="C11" s="68">
         <v>5</v>
       </c>
       <c r="D11" s="5"/>
@@ -3601,12 +3703,12 @@
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="4"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="17"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="12"/>
     </row>
     <row r="12" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C12" s="12">
+      <c r="C12" s="68">
         <v>6</v>
       </c>
       <c r="D12" s="5"/>
@@ -3616,12 +3718,12 @@
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="4"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="17"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="12"/>
     </row>
     <row r="13" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C13" s="12">
+      <c r="C13" s="68">
         <v>7</v>
       </c>
       <c r="D13" s="5"/>
@@ -3631,12 +3733,12 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="4"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="17"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="12"/>
     </row>
     <row r="14" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C14" s="12">
+      <c r="C14" s="68">
         <v>8</v>
       </c>
       <c r="D14" s="5"/>
@@ -3646,12 +3748,12 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="4"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="17"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="12"/>
     </row>
     <row r="15" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="12">
+      <c r="C15" s="68">
         <v>9</v>
       </c>
       <c r="D15" s="5"/>
@@ -3661,12 +3763,12 @@
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="4"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="17"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="12"/>
     </row>
     <row r="16" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="12">
+      <c r="C16" s="68">
         <v>10</v>
       </c>
       <c r="D16" s="5"/>
@@ -3676,12 +3778,12 @@
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="4"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="17"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="12"/>
     </row>
     <row r="17" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C17" s="12">
+      <c r="C17" s="68">
         <v>11</v>
       </c>
       <c r="D17" s="5"/>
@@ -3691,12 +3793,12 @@
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="4"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="17"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="12"/>
     </row>
     <row r="18" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C18" s="12">
+      <c r="C18" s="68">
         <v>12</v>
       </c>
       <c r="D18" s="5"/>
@@ -3706,12 +3808,12 @@
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="4"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="17"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="12"/>
     </row>
     <row r="19" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C19" s="12">
+      <c r="C19" s="68">
         <v>13</v>
       </c>
       <c r="D19" s="5"/>
@@ -3721,12 +3823,12 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="4"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="17"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="12"/>
     </row>
     <row r="20" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C20" s="12">
+      <c r="C20" s="68">
         <v>14</v>
       </c>
       <c r="D20" s="5"/>
@@ -3736,12 +3838,12 @@
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="4"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="17"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="12"/>
     </row>
     <row r="21" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C21" s="12">
+      <c r="C21" s="68">
         <v>15</v>
       </c>
       <c r="D21" s="5"/>
@@ -3751,12 +3853,12 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="4"/>
-      <c r="K21" s="11"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="17"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="12"/>
     </row>
     <row r="22" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C22" s="12">
+      <c r="C22" s="68">
         <v>16</v>
       </c>
       <c r="D22" s="5"/>
@@ -3766,12 +3868,12 @@
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="4"/>
-      <c r="K22" s="11"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="17"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="12"/>
     </row>
     <row r="23" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C23" s="12">
+      <c r="C23" s="68">
         <v>17</v>
       </c>
       <c r="D23" s="5"/>
@@ -3781,12 +3883,12 @@
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="4"/>
-      <c r="K23" s="11"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="17"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="12"/>
     </row>
     <row r="24" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C24" s="12">
+      <c r="C24" s="68">
         <v>18</v>
       </c>
       <c r="D24" s="5"/>
@@ -3796,12 +3898,12 @@
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="4"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="17"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="12"/>
     </row>
     <row r="25" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C25" s="12">
+      <c r="C25" s="68">
         <v>19</v>
       </c>
       <c r="D25" s="5"/>
@@ -3811,12 +3913,12 @@
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="4"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="17"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="12"/>
     </row>
     <row r="26" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C26" s="12">
+      <c r="C26" s="68">
         <v>20</v>
       </c>
       <c r="D26" s="5"/>
@@ -3826,12 +3928,12 @@
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="4"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="17"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="12"/>
     </row>
     <row r="27" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C27" s="12">
+      <c r="C27" s="68">
         <v>21</v>
       </c>
       <c r="D27" s="5"/>
@@ -3841,12 +3943,12 @@
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="4"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="17"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="12"/>
     </row>
     <row r="28" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C28" s="12">
+      <c r="C28" s="68">
         <v>22</v>
       </c>
       <c r="D28" s="5"/>
@@ -3856,145 +3958,115 @@
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="4"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="17"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="12"/>
     </row>
     <row r="29" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="12">
+      <c r="C29" s="69">
         <v>23</v>
       </c>
-      <c r="D29" s="5"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="17"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="36"/>
+      <c r="L29" s="37"/>
+      <c r="M29" s="38"/>
     </row>
     <row r="30" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="21">
-        <f t="shared" ref="D30:J30" si="0">SUM(D6:D29)</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F30" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G30" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="24">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K30" s="25">
-        <f>MAX(K6:K29)</f>
-        <v>0</v>
-      </c>
-      <c r="L30" s="26" t="e">
-        <f>AVERAGE(L6:L29)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M30" s="25">
-        <f>MIN(M6:M29)</f>
-        <v>0</v>
-      </c>
+      <c r="D30" s="13"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="39"/>
+      <c r="M30" s="40"/>
     </row>
     <row r="31" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="K31" s="29"/>
-      <c r="L31" s="29"/>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17"/>
       <c r="M31" s="2"/>
     </row>
     <row r="32" spans="3:14" ht="15.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1"/>
-      <c r="D32" s="42" t="s">
+      <c r="D32" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="43"/>
-      <c r="I32" s="42" t="s">
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="72"/>
+      <c r="I32" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="J32" s="37"/>
-      <c r="K32" s="37"/>
-      <c r="L32" s="43"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="72"/>
       <c r="N32" s="2"/>
     </row>
     <row r="33" spans="3:22" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="1"/>
-      <c r="D33" s="61" t="s">
+      <c r="D33" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="45"/>
-      <c r="I33" s="27" t="s">
+      <c r="E33" s="42"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="24"/>
+      <c r="I33" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="J33" s="35"/>
-      <c r="K33" s="53" t="s">
+      <c r="J33" s="19"/>
+      <c r="K33" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="L33" s="54"/>
+      <c r="L33" s="30"/>
     </row>
     <row r="34" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C34" s="1"/>
-      <c r="D34" s="60" t="s">
+      <c r="D34" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="E34" s="55"/>
-      <c r="F34" s="55"/>
-      <c r="G34" s="56"/>
-      <c r="I34" s="31" t="s">
+      <c r="E34" s="44"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="26"/>
+      <c r="I34" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="J34" s="11"/>
-      <c r="K34" s="38" t="s">
+      <c r="J34" s="8"/>
+      <c r="K34" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="L34" s="39"/>
+      <c r="L34" s="32"/>
     </row>
     <row r="35" spans="3:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C35" s="1"/>
-      <c r="D35" s="59" t="s">
+      <c r="D35" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="57"/>
-      <c r="F35" s="57"/>
-      <c r="G35" s="58"/>
-      <c r="I35" s="28" t="s">
+      <c r="E35" s="46"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="28"/>
+      <c r="I35" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="J35" s="36"/>
-      <c r="K35" s="40" t="s">
+      <c r="J35" s="20"/>
+      <c r="K35" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="L35" s="41"/>
+      <c r="L35" s="22"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
-      <c r="P35" s="30"/>
+      <c r="P35" s="18"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
@@ -4026,7 +4098,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>

--- a/public/report/DayReport.xlsx
+++ b/public/report/DayReport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hdrenewables-my.sharepoint.com/personal/hugo_huang_hdrenewables_com/Documents/2.案場資料/1.專案開發/3.表前-花蓮三案/E-dReg-10M+10M/8.報表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="6_{DCBEEB1A-7347-4214-9C4B-83766357FDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43C1C5AB-6750-4881-99C3-B9BBAF8D97BA}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="6_{DCBEEB1A-7347-4214-9C4B-83766357FDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1779675-5C06-40F4-B2F3-1BA9D2713F0F}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-190" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日報" sheetId="2" r:id="rId1"/>
@@ -143,7 +143,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>花蓮和平10MW</t>
+    <t>花蓮和平10MW 地號4-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -799,42 +799,6 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -859,24 +823,6 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -888,65 +834,119 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3537,7 +3537,7 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.7109375" style="1"/>
-    <col min="3" max="3" width="8.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.42578125" style="2" customWidth="1"/>
     <col min="4" max="10" width="6.42578125" style="2" customWidth="1"/>
     <col min="11" max="11" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.42578125" style="1" customWidth="1"/>
@@ -3547,78 +3547,78 @@
   <sheetData>
     <row r="2" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="3:13" ht="15.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51" t="s">
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="51"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="51" t="s">
+      <c r="G3" s="33"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="51"/>
-      <c r="M3" s="53"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="34"/>
     </row>
     <row r="4" spans="3:13" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="55" t="s">
+      <c r="D4" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="54" t="s">
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="71"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="L4" s="58"/>
-      <c r="M4" s="59"/>
+      <c r="L4" s="57"/>
+      <c r="M4" s="58"/>
     </row>
     <row r="5" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="60"/>
-      <c r="D5" s="61">
+      <c r="C5" s="69"/>
+      <c r="D5" s="35">
         <v>1</v>
       </c>
-      <c r="E5" s="62">
+      <c r="E5" s="36">
         <v>0.8</v>
       </c>
-      <c r="F5" s="62">
+      <c r="F5" s="36">
         <v>0.6</v>
       </c>
-      <c r="G5" s="62">
+      <c r="G5" s="36">
         <v>0.4</v>
       </c>
-      <c r="H5" s="62">
+      <c r="H5" s="36">
         <v>0.2</v>
       </c>
-      <c r="I5" s="62">
+      <c r="I5" s="36">
         <v>0</v>
       </c>
-      <c r="J5" s="63">
+      <c r="J5" s="37">
         <v>-1</v>
       </c>
-      <c r="K5" s="64" t="s">
+      <c r="K5" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="L5" s="65" t="s">
+      <c r="L5" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="M5" s="66" t="s">
+      <c r="M5" s="40" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C6" s="67">
+      <c r="C6" s="41">
         <v>0</v>
       </c>
       <c r="D6" s="9"/>
@@ -3633,7 +3633,7 @@
       <c r="M6" s="12"/>
     </row>
     <row r="7" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C7" s="68">
+      <c r="C7" s="42">
         <v>1</v>
       </c>
       <c r="D7" s="5"/>
@@ -3648,7 +3648,7 @@
       <c r="M7" s="12"/>
     </row>
     <row r="8" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C8" s="68">
+      <c r="C8" s="42">
         <v>2</v>
       </c>
       <c r="D8" s="5"/>
@@ -3663,7 +3663,7 @@
       <c r="M8" s="12"/>
     </row>
     <row r="9" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C9" s="68">
+      <c r="C9" s="42">
         <v>3</v>
       </c>
       <c r="D9" s="5"/>
@@ -3678,7 +3678,7 @@
       <c r="M9" s="12"/>
     </row>
     <row r="10" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C10" s="68">
+      <c r="C10" s="42">
         <v>4</v>
       </c>
       <c r="D10" s="5"/>
@@ -3693,7 +3693,7 @@
       <c r="M10" s="12"/>
     </row>
     <row r="11" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C11" s="68">
+      <c r="C11" s="42">
         <v>5</v>
       </c>
       <c r="D11" s="5"/>
@@ -3708,7 +3708,7 @@
       <c r="M11" s="12"/>
     </row>
     <row r="12" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C12" s="68">
+      <c r="C12" s="42">
         <v>6</v>
       </c>
       <c r="D12" s="5"/>
@@ -3723,7 +3723,7 @@
       <c r="M12" s="12"/>
     </row>
     <row r="13" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C13" s="68">
+      <c r="C13" s="42">
         <v>7</v>
       </c>
       <c r="D13" s="5"/>
@@ -3738,7 +3738,7 @@
       <c r="M13" s="12"/>
     </row>
     <row r="14" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C14" s="68">
+      <c r="C14" s="42">
         <v>8</v>
       </c>
       <c r="D14" s="5"/>
@@ -3753,7 +3753,7 @@
       <c r="M14" s="12"/>
     </row>
     <row r="15" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="68">
+      <c r="C15" s="42">
         <v>9</v>
       </c>
       <c r="D15" s="5"/>
@@ -3768,7 +3768,7 @@
       <c r="M15" s="12"/>
     </row>
     <row r="16" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="68">
+      <c r="C16" s="42">
         <v>10</v>
       </c>
       <c r="D16" s="5"/>
@@ -3783,7 +3783,7 @@
       <c r="M16" s="12"/>
     </row>
     <row r="17" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C17" s="68">
+      <c r="C17" s="42">
         <v>11</v>
       </c>
       <c r="D17" s="5"/>
@@ -3798,7 +3798,7 @@
       <c r="M17" s="12"/>
     </row>
     <row r="18" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C18" s="68">
+      <c r="C18" s="42">
         <v>12</v>
       </c>
       <c r="D18" s="5"/>
@@ -3813,7 +3813,7 @@
       <c r="M18" s="12"/>
     </row>
     <row r="19" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C19" s="68">
+      <c r="C19" s="42">
         <v>13</v>
       </c>
       <c r="D19" s="5"/>
@@ -3828,7 +3828,7 @@
       <c r="M19" s="12"/>
     </row>
     <row r="20" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C20" s="68">
+      <c r="C20" s="42">
         <v>14</v>
       </c>
       <c r="D20" s="5"/>
@@ -3843,7 +3843,7 @@
       <c r="M20" s="12"/>
     </row>
     <row r="21" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C21" s="68">
+      <c r="C21" s="42">
         <v>15</v>
       </c>
       <c r="D21" s="5"/>
@@ -3858,7 +3858,7 @@
       <c r="M21" s="12"/>
     </row>
     <row r="22" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C22" s="68">
+      <c r="C22" s="42">
         <v>16</v>
       </c>
       <c r="D22" s="5"/>
@@ -3873,7 +3873,7 @@
       <c r="M22" s="12"/>
     </row>
     <row r="23" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C23" s="68">
+      <c r="C23" s="42">
         <v>17</v>
       </c>
       <c r="D23" s="5"/>
@@ -3888,7 +3888,7 @@
       <c r="M23" s="12"/>
     </row>
     <row r="24" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C24" s="68">
+      <c r="C24" s="42">
         <v>18</v>
       </c>
       <c r="D24" s="5"/>
@@ -3903,7 +3903,7 @@
       <c r="M24" s="12"/>
     </row>
     <row r="25" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C25" s="68">
+      <c r="C25" s="42">
         <v>19</v>
       </c>
       <c r="D25" s="5"/>
@@ -3918,7 +3918,7 @@
       <c r="M25" s="12"/>
     </row>
     <row r="26" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C26" s="68">
+      <c r="C26" s="42">
         <v>20</v>
       </c>
       <c r="D26" s="5"/>
@@ -3933,7 +3933,7 @@
       <c r="M26" s="12"/>
     </row>
     <row r="27" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C27" s="68">
+      <c r="C27" s="42">
         <v>21</v>
       </c>
       <c r="D27" s="5"/>
@@ -3948,7 +3948,7 @@
       <c r="M27" s="12"/>
     </row>
     <row r="28" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C28" s="68">
+      <c r="C28" s="42">
         <v>22</v>
       </c>
       <c r="D28" s="5"/>
@@ -3963,22 +3963,22 @@
       <c r="M28" s="12"/>
     </row>
     <row r="29" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="69">
+      <c r="C29" s="43">
         <v>23</v>
       </c>
-      <c r="D29" s="33"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="34"/>
-      <c r="J29" s="35"/>
-      <c r="K29" s="36"/>
-      <c r="L29" s="37"/>
-      <c r="M29" s="38"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
+      <c r="J29" s="23"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="26"/>
     </row>
     <row r="30" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="70" t="s">
+      <c r="C30" s="44" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="13"/>
@@ -3989,8 +3989,8 @@
       <c r="I30" s="14"/>
       <c r="J30" s="15"/>
       <c r="K30" s="16"/>
-      <c r="L30" s="39"/>
-      <c r="M30" s="40"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="28"/>
     </row>
     <row r="31" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K31" s="17"/>
@@ -3999,70 +3999,70 @@
     </row>
     <row r="32" spans="3:14" ht="15.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1"/>
-      <c r="D32" s="71" t="s">
+      <c r="D32" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="72"/>
-      <c r="I32" s="71" t="s">
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="49"/>
+      <c r="I32" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="J32" s="52"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="72"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="48"/>
+      <c r="L32" s="49"/>
       <c r="N32" s="2"/>
     </row>
     <row r="33" spans="3:22" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="1"/>
-      <c r="D33" s="41" t="s">
+      <c r="D33" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="E33" s="42"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="24"/>
-      <c r="I33" s="47" t="s">
+      <c r="E33" s="68"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="51"/>
+      <c r="I33" s="29" t="s">
         <v>12</v>
       </c>
       <c r="J33" s="19"/>
-      <c r="K33" s="29" t="s">
+      <c r="K33" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="L33" s="30"/>
+      <c r="L33" s="60"/>
     </row>
     <row r="34" spans="3:22" x14ac:dyDescent="0.25">
       <c r="C34" s="1"/>
-      <c r="D34" s="43" t="s">
+      <c r="D34" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="E34" s="44"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="26"/>
-      <c r="I34" s="48" t="s">
+      <c r="E34" s="66"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="53"/>
+      <c r="I34" s="30" t="s">
         <v>13</v>
       </c>
       <c r="J34" s="8"/>
-      <c r="K34" s="31" t="s">
+      <c r="K34" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="L34" s="32"/>
+      <c r="L34" s="62"/>
     </row>
     <row r="35" spans="3:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C35" s="1"/>
-      <c r="D35" s="45" t="s">
+      <c r="D35" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="46"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="28"/>
-      <c r="I35" s="49" t="s">
+      <c r="E35" s="64"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="55"/>
+      <c r="I35" s="31" t="s">
         <v>14</v>
       </c>
       <c r="J35" s="20"/>
-      <c r="K35" s="21" t="s">
+      <c r="K35" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="L35" s="22"/>
+      <c r="L35" s="46"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>

--- a/public/report/DayReport.xlsx
+++ b/public/report/DayReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hdrenewables-my.sharepoint.com/personal/hugo_huang_hdrenewables_com/Documents/2.案場資料/1.專案開發/3.表前-花蓮三案/E-dReg-10M+10M/8.報表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="6_{DCBEEB1A-7347-4214-9C4B-83766357FDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1779675-5C06-40F4-B2F3-1BA9D2713F0F}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="6_{DCBEEB1A-7347-4214-9C4B-83766357FDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93F90BEB-32FA-4860-BB66-90BD7F9A0E1A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
